--- a/stories/arbres/ATOM-SOC.PAY.001-01.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Inès s'assoit sur le tapis, près de papa. Papa ouvre un grand livre. Les pages sentent le papier. Papa dit : on va nommer un pays. Inès pose le doigt. Papa lit le nom : la France. Inès répète : la France. Sur la page, il y a de l'eau bleue. Des vagues. Du sable. Papa dit : ça, c'est un paysage. C'est la mer. Inès dit : la mer. Elle entend presque le bruit des vagues. Papa tourne encore. Des sommets blancs. Papa dit : ça aussi, c'est un paysage. C'est la montagne. Inès dit : la montagne. Un pays. Un nom. Un paysage. La France, et la mer. Papa ferme le livre. Inès le range sur la table basse.</t>
+          <t>Inès s'assoit sur le tapis, près de papa. Papa ouvre un grand livre. Les pages sentent le papier. On va nommer un pays. Inès pose le doigt. Papa lit le nom : la France. Inès répète : la France. Sur la page, il y a de l'eau bleue. Des vagues. Du sable. Ça, c'est un paysage. C'est la mer. La mer. Elle entend presque le bruit des vagues. Papa tourne encore. Des sommets blancs. Ça aussi, c'est un paysage. C'est la montagne. La montagne. Un pays. Un nom. Un paysage. La France, et la mer. Papa ferme le livre. Inès le range sur la table basse.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Inès s'assoit sur le tapis, près de papa. Papa ouvre un grand livre. Les pages sentent le papier.
+papa|On va nommer un pays.
+narrateur|Inès pose le doigt. Papa lit le nom : la France. Inès répète : la France. Sur la page, il y a de l'eau bleue. Des vagues. Du sable.
+papa|Ça, c'est un paysage. C'est la mer.
+enfant-f|La mer. Elle entend presque le bruit des vagues. Papa tourne encore. Des sommets blancs.
+papa|Ça aussi, c'est un paysage. C'est la montagne.
+enfant-f|La montagne.
+narrateur|Un pays. Un nom. Un paysage. La France, et la mer. Papa ferme le livre. Inès le range sur la table basse.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1497,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Inès nomme la France. Elle nomme aussi quoi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1670,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a dit le nom. La France. Elle a dit le paysage. La mer. La montagne aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Inès s'allonge près de papa. Elle ferme les yeux. Elle pense à l'eau salée.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.PAY.001-01.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 narrateur|Un pays. Un nom. Un paysage. La France, et la mer. Papa ferme le livre. Inès le range sur la table basse.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1504,6 +1510,7 @@
           <t>narrateur|Inès nomme la France. Elle nomme aussi quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1675,6 +1682,7 @@
           <t>narrateur|Inès a dit le nom. La France. Elle a dit le paysage. La mer. La montagne aussi.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1846,7 @@
           <t>narrateur|Inès s'allonge près de papa. Elle ferme les yeux. Elle pense à l'eau salée.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.PAY.001-01.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La mer de France d'Inès</t>
+          <t>Le coquillage sous le tapis</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Aniss veut entendre les vagues dans le coquillage. Papa déplie la France, le bleu de la mer. Le coquillage file sous le tapis. Aniss le trouve, l'écoute, garde la main sur la carte.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Inès s'assoit sur le tapis, près de papa. Papa ouvre un grand livre. Les pages sentent le papier. On va nommer un pays. Inès pose le doigt. Papa lit le nom : la France. Inès répète : la France. Sur la page, il y a de l'eau bleue. Des vagues. Du sable. Ça, c'est un paysage. C'est la mer. La mer. Elle entend presque le bruit des vagues. Papa tourne encore. Des sommets blancs. Ça aussi, c'est un paysage. C'est la montagne. La montagne. Un pays. Un nom. Un paysage. La France, et la mer. Papa ferme le livre. Inès le range sur la table basse.</t>
+          <t>La carte de France dépasse du tapis bleu. Les plis sont usés, un peu brillants. Un coquillage blanc attend près du livre. Il sent encore un peu le sel, tout loin. Aniss vit ici, avec papa. La fenêtre est ouverte, sans vague. Je veux entendre la mer, papa. Avec le coquillage ? Oui. Et voir les vagues. On pose le doigt sur la carte, d'abord. En ce moment, Aniss s'assoit en tailleur. Le tapis gratte un peu les genoux. Papa déplie un grand bleu, sur la gauche. Ça, c'est la France. La France. Et ce bleu, c'est la mer. La mer de France. Les vagues sont là ? Sur la carte, c'est tout calme. Dans le coquillage, on peut les imaginer. Aniss tend la main vers le coquillage. Le coquillage roule. Il file sous le tapis, tout de suite. Il s'est caché ! Sous le tapis ? Oui. On soulève le bord, tout doux ? Le tapis est lourd, un peu rêche. Une poussière danse dans le rayon. Je ne le vois pas. Plus loin, peut-être. On cherche ensemble. Aniss glisse la main, paume ouverte. Le tapis sent la laine tiède. Rien, d'abord, sauf un fil. Tu entends encore la mer, sans lui ? Non. Je veux le coquillage.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Inès s'assoit sur le tapis, près de papa. Papa ouvre un grand livre. Les pages sentent le papier. Papa dit : on va &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;mer un pays. Inès pose le doigt. Papa lit le nom : la France. Inès répète : la France. Sur la page, il y a de l'eau bleue. Des vagues. Du sable. Papa dit : ça, c'est un paysage. C'est la mer. Inès dit : la mer. Elle entend presque le bruit des vagues. Papa tourne encore. Des sommets blancs. Papa dit : ça aussi, c'est un paysage. C'est la montagne. Inès dit : la montagne. Un pays. Un nom. Un paysage. La France, et la mer. Papa ferme le livre. Inès le range sur la table basse.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La carte de France dépasse du tapis bleu. Les plis sont usés, un peu brillants. Un coquillage blanc attend près du livre. Il sent encore un peu le sel, tout loin. Aniss vit ici, avec papa. La fenêtre est ouverte, sans vague. Je veux entendre la mer, papa. Avec le coquillage ? Oui. Et voir les vagues. On pose le doigt sur la carte, d'abord. En ce moment, Aniss s'assoit en tailleur. Le tapis gratte un peu les genoux. Papa déplie un grand bleu, sur la gauche. Ça, c'est la France. La France. Et ce bleu, c'est la mer. La mer de France. Les vagues sont là ? Sur la carte, c'est tout calme. Dans le coquillage, on peut les imaginer. Aniss tend la main vers le coquillage. Le coquillage roule. Il file sous le tapis, tout de suite. Il s'est caché ! Sous le tapis ? Oui. On soulève le bord, tout doux ? Le tapis est lourd, un peu rêche. Une poussière danse dans le rayon. Je ne le vois pas. Plus loin, peut-être. On cherche ensemble. Aniss glisse la main, paume ouverte. Le tapis sent la laine tiède. Rien, d'abord, sauf un fil. Tu entends encore la mer, sans lui ? Non. Je veux le coquillage.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,17 +1324,47 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Inès s'assoit sur le tapis, près de papa. Papa ouvre un grand livre. Les pages sentent le papier.
-papa|On va nommer un pays.
-narrateur|Inès pose le doigt. Papa lit le nom : la France. Inès répète : la France. Sur la page, il y a de l'eau bleue. Des vagues. Du sable.
-papa|Ça, c'est un paysage. C'est la mer.
-enfant-f|La mer. Elle entend presque le bruit des vagues. Papa tourne encore. Des sommets blancs.
-papa|Ça aussi, c'est un paysage. C'est la montagne.
-enfant-f|La montagne.
-narrateur|Un pays. Un nom. Un paysage. La France, et la mer. Papa ferme le livre. Inès le range sur la table basse.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La carte de France dépasse du tapis bleu.
+narrateur|Les plis sont usés, un peu brillants.
+narrateur|Un coquillage blanc attend près du livre.
+narrateur|Il sent encore un peu le sel, tout loin.
+narrateur|Aniss vit ici, avec papa.
+narrateur|La fenêtre est ouverte, sans vague.
+enfant-m|Je veux entendre la mer, papa.
+papa|Avec le coquillage ?
+enfant-m|Oui.
+enfant-m|Et voir les vagues.
+papa|On pose le doigt sur la carte, d'abord.
+narrateur|En ce moment, Aniss s'assoit en tailleur.
+narrateur|Le tapis gratte un peu les genoux.
+narrateur|Papa déplie un grand bleu, sur la gauche.
+papa|Ça, c'est la France.
+enfant-m|La France.
+papa|Et ce bleu, c'est la mer.
+papa|La mer de France.
+enfant-m|Les vagues sont là ?
+papa|Sur la carte, c'est tout calme.
+papa|Dans le coquillage, on peut les imaginer.
+narrateur|Aniss tend la main vers le coquillage.
+narrateur|Le coquillage roule.
+narrateur|Il file sous le tapis, tout de suite.
+enfant-m|Il s'est caché !
+papa|Sous le tapis ?
+enfant-m|Oui.
+papa|On soulève le bord, tout doux ?
+narrateur|Le tapis est lourd, un peu rêche.
+narrateur|Une poussière danse dans le rayon.
+enfant-m|Je ne le vois pas.
+papa|Plus loin, peut-être.
+papa|On cherche ensemble.
+narrateur|Aniss glisse la main, paume ouverte.
+narrateur|Le tapis sent la laine tiède.
+narrateur|Rien, d'abord, sauf un fil.
+papa|Tu entends encore la mer, sans lui ?
+enfant-m|Non.
+enfant-m|Je veux le coquillage.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1347,12 +1389,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Inès nomme la France. Elle nomme aussi quoi ?</t>
+          <t>Aniss nomme la France. Il nomme aussi quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Inès &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;me la France. Elle nomme aussi quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss nomme la France. Il nomme aussi quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1362,12 +1404,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>la mer</t>
+          <t>mer</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>la mer | un paysage | un pays | la France</t>
+          <t>mer | la mer | le mer | vagues | la mer de France | paysage</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1382,7 +1424,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il y a de l'eau bleue. C'est quel paysage ?</t>
+          <t>Sur la carte, le bleu, c'est quoi ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1431,7 +1473,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1507,10 +1549,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Inès nomme la France. Elle nomme aussi quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Aniss nomme la France.
+narrateur|Il nomme aussi quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1535,12 +1577,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Inès a dit le nom. La France. Elle a dit le paysage. La mer. La montagne aussi.</t>
+          <t>Les doigts d'Aniss touchent une bosse dure. Le coquillage est là, sous la laine. Je l'ai ! Bravo, Aniss. Tu l'as trouvé. Il est un peu tiède, un peu poussiéreux. Papa souffle, tout doux. La poussière part vers la fenêtre. Je l'écoute. Contre l'oreille. Aniss pose le coquillage. Un souffle lointain, comme une vague petite. J'entends la mer ! La mer de France. Le bleu, sur la carte. Les vagues. Tu les entends, dedans. Merci d'avoir cherché sous le tapis. Le bord du tapis retombe, tout plat. La France reste ouverte, avec son bleu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Inès a dit le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;. La France. Elle a dit le paysage. La mer. La montagne aussi.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les doigts d'Aniss touchent une bosse dure. Le coquillage est là, sous la laine. Je l'ai ! Bravo, Aniss. Tu l'as trouvé. Il est un peu tiède, un peu poussiéreux. Papa souffle, tout doux. La poussière part vers la fenêtre. Je l'écoute. Contre l'oreille. Aniss pose le coquillage. Un souffle lointain, comme une vague petite. J'entends la mer ! La mer de France. Le bleu, sur la carte. Les vagues. Tu les entends, dedans. Merci d'avoir cherché sous le tapis. Le bord du tapis retombe, tout plat. La France reste ouverte, avec son bleu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1603,7 +1645,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1679,10 +1721,28 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Inès a dit le nom. La France. Elle a dit le paysage. La mer. La montagne aussi.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Les doigts d'Aniss touchent une bosse dure.
+narrateur|Le coquillage est là, sous la laine.
+enfant-m|Je l'ai !
+papa|Bravo, Aniss.
+papa|Tu l'as trouvé.
+narrateur|Il est un peu tiède, un peu poussiéreux.
+narrateur|Papa souffle, tout doux.
+narrateur|La poussière part vers la fenêtre.
+enfant-m|Je l'écoute.
+papa|Contre l'oreille.
+narrateur|Aniss pose le coquillage.
+narrateur|Un souffle lointain, comme une vague petite.
+enfant-m|J'entends la mer !
+papa|La mer de France.
+papa|Le bleu, sur la carte.
+enfant-m|Les vagues.
+papa|Tu les entends, dedans.
+papa|Merci d'avoir cherché sous le tapis.
+narrateur|Le bord du tapis retombe, tout plat.
+narrateur|La France reste ouverte, avec son bleu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1707,12 +1767,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Inès s'allonge près de papa. Elle ferme les yeux. Elle pense à l'eau salée.</t>
+          <t>Aniss garde le coquillage contre l'oreille. L'autre main reste sur le bleu de la carte. Ça chante, papa. Oui. Même ici, sans le vent du port. Tu veux que je nomme encore ? La France. Et la mer. Un pays, un paysage. Papa replie un coin de carte, pas trop. Le bleu reste visible, comme une porte. Je referme les yeux. Les vagues sont là, dedans. Le tapis ne cache plus rien. Juste la laine, et les genoux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Inès s'allonge près de papa. Elle ferme les yeux. Elle pense à l'eau salée.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss garde le coquillage contre l'oreille. L'autre main reste sur le bleu de la carte. Ça chante, papa. Oui. Même ici, sans le vent du port. Tu veux que je nomme encore ? La France. Et la mer. Un pays, un paysage. Papa replie un coin de carte, pas trop. Le bleu reste visible, comme une porte. Je referme les yeux. Les vagues sont là, dedans. Le tapis ne cache plus rien. Juste la laine, et les genoux.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1775,7 +1835,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1843,10 +1903,23 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Inès s'allonge près de papa. Elle ferme les yeux. Elle pense à l'eau salée.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Aniss garde le coquillage contre l'oreille.
+narrateur|L'autre main reste sur le bleu de la carte.
+enfant-m|Ça chante, papa.
+papa|Oui.
+papa|Même ici, sans le vent du port.
+papa|Tu veux que je nomme encore ?
+enfant-m|La France.
+enfant-m|Et la mer.
+papa|Un pays, un paysage.
+narrateur|Papa replie un coin de carte, pas trop.
+narrateur|Le bleu reste visible, comme une porte.
+enfant-m|Je referme les yeux.
+papa|Les vagues sont là, dedans.
+narrateur|Le tapis ne cache plus rien.
+narrateur|Juste la laine, et les genoux.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1871,12 +1944,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le coquillage reste au creux de la main. Le souffle lointain continue, tout petit. La mer est là. Oui. La mer de France, sur le tapis. La fenêtre n'a toujours pas de vague. Aniss en a une, contre l'oreille, quand même.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le coquillage reste au creux de la main. Le souffle lointain continue, tout petit. La mer est là. Oui. La mer de France, sur le tapis. La fenêtre n'a toujours pas de vague. Aniss en a une, contre l'oreille, quand même.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1932,14 +2005,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2011,10 +2084,15 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le coquillage reste au creux de la main.
+narrateur|Le souffle lointain continue, tout petit.
+enfant-m|La mer est là.
+papa|Oui.
+papa|La mer de France, sur le tapis.
+narrateur|La fenêtre n'a toujours pas de vague.
+narrateur|Aniss en a une, contre l'oreille, quand même.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2033,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2149,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.PAY.001-01.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon</t>
+          <t>salon, tapis bleu, carte de France, fenêtre ouverte</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Inès, papa</t>
+          <t>Aniss, papa</t>
         </is>
       </c>
     </row>
